--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-administration-de-derives-du-sang.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-administration-de-derives-du-sang.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="340">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -830,6 +830,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7343,7 +7347,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7351,10 +7355,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7380,10 +7384,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7414,7 +7418,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7432,7 +7436,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7452,10 +7456,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7553,10 +7557,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7597,7 +7601,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7656,10 +7660,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7759,10 +7763,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7862,10 +7866,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7965,10 +7969,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8068,10 +8072,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8169,10 +8173,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8270,10 +8274,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8373,10 +8377,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8476,10 +8480,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8579,10 +8583,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8605,13 +8609,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8662,7 +8666,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8682,10 +8686,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8708,7 +8712,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8741,7 +8745,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8759,7 +8763,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8779,10 +8783,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8805,7 +8809,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8858,7 +8862,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8878,10 +8882,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8937,25 +8941,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8975,10 +8979,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9001,10 +9005,10 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -9056,7 +9060,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9076,10 +9080,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9102,7 +9106,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9135,25 +9139,25 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9173,10 +9177,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9199,7 +9203,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9232,25 +9236,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9270,10 +9274,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9300,7 +9304,7 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9351,7 +9355,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9371,10 +9375,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9397,7 +9401,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9450,7 +9454,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9470,10 +9474,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9496,7 +9500,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9549,7 +9553,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9569,10 +9573,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9595,7 +9599,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9648,7 +9652,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9668,10 +9672,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9694,7 +9698,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9747,7 +9751,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9767,10 +9771,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9793,7 +9797,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9846,7 +9850,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9866,10 +9870,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9892,7 +9896,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9945,7 +9949,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9965,10 +9969,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9991,7 +9995,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10044,7 +10048,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10064,10 +10068,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10090,7 +10094,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10143,7 +10147,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10163,10 +10167,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10189,7 +10193,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10242,7 +10246,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10262,10 +10266,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10288,7 +10292,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10341,7 +10345,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10361,10 +10365,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10387,11 +10391,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10442,7 +10446,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10462,10 +10466,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10563,10 +10567,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10664,10 +10668,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10765,10 +10769,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10866,10 +10870,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10969,10 +10973,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11072,10 +11076,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11175,10 +11179,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11278,10 +11282,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11379,10 +11383,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11416,7 +11420,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>74</v>
@@ -11438,7 +11442,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11456,7 +11460,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11476,10 +11480,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11502,7 +11506,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11555,7 +11559,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -11575,10 +11579,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11601,7 +11605,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11654,7 +11658,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
